--- a/Cost model - Electrolyte support.xlsx
+++ b/Cost model - Electrolyte support.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/fskna_dtu_dk/Documents/Papers DTU Energy/Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{21B2C352-9AF5-40C8-9F2A-874D10761F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{357A82BF-BD53-4914-9045-9207EA022546}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{21B2C352-9AF5-40C8-9F2A-874D10761F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E639B10-2586-4BC0-9A10-9161CE478354}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B800C1E-3020-450D-98CF-85AAE588E4EC}"/>
+    <workbookView xWindow="3150" yWindow="3660" windowWidth="28800" windowHeight="15345" xr2:uid="{6B800C1E-3020-450D-98CF-85AAE588E4EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Manufacturing results" sheetId="8" r:id="rId1"/>
@@ -25,9 +25,6 @@
     <sheet name="LHV" sheetId="15" r:id="rId10"/>
     <sheet name="Calculations" sheetId="5" r:id="rId11"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId12"/>
-  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1221,8 +1218,8 @@
     <numFmt numFmtId="169" formatCode="0.0000"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
     <numFmt numFmtId="171" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;????_-;_-@_-"/>
-    <numFmt numFmtId="174" formatCode="0.0%"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;????_-;_-@_-"/>
+    <numFmt numFmtId="173" formatCode="0.0%"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -1505,7 +1502,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1565,7 +1562,7 @@
     <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="5"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
@@ -1573,7 +1570,7 @@
     <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1590,12 +1587,7 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="173" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -8414,44 +8406,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls driveId="b!HevMbQHv00anX2DZUNe2mUFWFOXyvk1Nla6BCD9qkcgE8H0-PG0XT7DtkIH1ANwO" itemId="01CIYPTOL3T7M43SIUJJEYUSXSDMA26CDG">
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Manufacturing results"/>
-      <sheetName val="Performance"/>
-      <sheetName val="Cross-layer"/>
-      <sheetName val="Manufacturing inputs"/>
-      <sheetName val="Cell"/>
-      <sheetName val="Frame"/>
-      <sheetName val="Misc"/>
-      <sheetName val="Manufacturing calc"/>
-      <sheetName val="Materials"/>
-      <sheetName val="LHV"/>
-      <sheetName val="Calculations"/>
-      <sheetName val="#REF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D31398C-93EA-46B9-98B2-EDA0AA84BB19}" name="Max_cycle_table" displayName="Max_cycle_table" ref="F1:J5" totalsRowShown="0">
   <autoFilter ref="F1:J5" xr:uid="{5D31398C-93EA-46B9-98B2-EDA0AA84BB19}"/>
@@ -11362,16 +11316,12 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="87"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
+      <c r="B12" s="18"/>
       <c r="I12" s="61" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="83"/>
       <c r="E13" t="s">
         <v>361</v>
       </c>
@@ -11394,7 +11344,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="87"/>
+      <c r="B14" s="18"/>
       <c r="E14" t="s">
         <v>365</v>
       </c>
@@ -11408,7 +11358,6 @@
       <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="83"/>
       <c r="E15" t="s">
         <v>369</v>
       </c>
@@ -11431,7 +11380,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="86"/>
+      <c r="B16" s="37"/>
       <c r="E16" t="s">
         <v>370</v>
       </c>
@@ -11453,8 +11402,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="83"/>
+    <row r="17" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
         <v>372</v>
       </c>
@@ -11476,7 +11424,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:11" x14ac:dyDescent="0.25">
       <c r="I18" t="s">
         <v>367</v>
       </c>
@@ -11488,7 +11436,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:11" x14ac:dyDescent="0.25">
       <c r="I19" t="s">
         <v>373</v>
       </c>
@@ -11500,45 +11448,45 @@
         <v>374</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:11" x14ac:dyDescent="0.25">
       <c r="J20" s="15"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:11" x14ac:dyDescent="0.25">
       <c r="I22" s="61"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E23" s="61"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F24" s="85"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F25" s="85"/>
+    <row r="24" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="F24" s="15"/>
+    </row>
+    <row r="25" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="F25" s="15"/>
       <c r="J25" s="57"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F26" s="84"/>
+    <row r="26" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="F26" s="8"/>
       <c r="J26" s="18"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E27" s="15"/>
-      <c r="F27" s="87"/>
+      <c r="F27" s="18"/>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F28" s="85"/>
+    <row r="28" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="F28" s="15"/>
       <c r="G28" s="37"/>
       <c r="J28" s="18"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F29" s="84"/>
+    <row r="29" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="F29" s="8"/>
       <c r="G29" s="37"/>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="5:11" x14ac:dyDescent="0.25">
       <c r="J30" s="15"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="5:11" x14ac:dyDescent="0.25">
       <c r="I32" s="61"/>
     </row>
     <row r="33" spans="10:10" x14ac:dyDescent="0.25">
@@ -15997,7 +15945,7 @@
         <v>90</v>
       </c>
       <c r="C5">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
